--- a/artfynd/A 1523-2023 artfynd.xlsx
+++ b/artfynd/A 1523-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125722229</v>
       </c>
       <c r="B2" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>125722231</v>
       </c>
       <c r="B5" t="n">
-        <v>58153</v>
+        <v>58154</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>125722234</v>
       </c>
       <c r="B6" t="n">
-        <v>58325</v>
+        <v>58326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1523-2023 artfynd.xlsx
+++ b/artfynd/A 1523-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125722229</v>
       </c>
       <c r="B2" t="n">
-        <v>57907</v>
+        <v>57908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>125722218</v>
       </c>
       <c r="B3" t="n">
-        <v>57562</v>
+        <v>57563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>125722213</v>
       </c>
       <c r="B4" t="n">
-        <v>57473</v>
+        <v>57474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>125722231</v>
       </c>
       <c r="B5" t="n">
-        <v>58154</v>
+        <v>58155</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>125722234</v>
       </c>
       <c r="B6" t="n">
-        <v>58326</v>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>125722221</v>
       </c>
       <c r="B7" t="n">
-        <v>57640</v>
+        <v>57641</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 1523-2023 artfynd.xlsx
+++ b/artfynd/A 1523-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125722229</v>
       </c>
       <c r="B2" t="n">
-        <v>57908</v>
+        <v>57912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>125722218</v>
       </c>
       <c r="B3" t="n">
-        <v>57563</v>
+        <v>57567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>125722213</v>
       </c>
       <c r="B4" t="n">
-        <v>57474</v>
+        <v>57478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>125722231</v>
       </c>
       <c r="B5" t="n">
-        <v>58155</v>
+        <v>58159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>125722234</v>
       </c>
       <c r="B6" t="n">
-        <v>58327</v>
+        <v>58331</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>125722221</v>
       </c>
       <c r="B7" t="n">
-        <v>57641</v>
+        <v>57645</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
